--- a/build/Position_Report_template.xlsx
+++ b/build/Position_Report_template.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="15480" yWindow="1103" windowWidth="19395" windowHeight="10995" activeTab="1"/>
+    <workbookView xWindow="15480" yWindow="1103" windowWidth="19395" windowHeight="10995" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="Summary Of Locos Not Active" sheetId="2" r:id="rId2"/>
-    <sheet name="Summary Of Locos with CDF" sheetId="4" r:id="rId3"/>
+    <sheet name="Summary Of Locos with C and F" sheetId="4" r:id="rId3"/>
     <sheet name="Each 2080 Received by BOS" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="145621"/>
@@ -96,9 +96,6 @@
     <t>Approx Time (UTC)</t>
   </si>
   <si>
-    <t>Summary Of Locomotives With "Cut-out" "Disengaged" "Failed"</t>
-  </si>
-  <si>
     <t>Number of Locos Not Transitioning to Active</t>
   </si>
   <si>
@@ -271,6 +268,9 @@
   </si>
   <si>
     <t>UP-321</t>
+  </si>
+  <si>
+    <t>Summary Of Locomotives with "Cut-out" and "Failed"</t>
   </si>
 </sst>
 </file>
@@ -499,66 +499,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -612,6 +552,66 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -922,142 +922,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
+      <c r="A1" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="18"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="18"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="37"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="37"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="18"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="37"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="18"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="37"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="18"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="18"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="37"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="18"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="18"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
     </row>
     <row r="11" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="21"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="40"/>
     </row>
     <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="9:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="9:9" x14ac:dyDescent="0.45">
       <c r="I28" s="2"/>
     </row>
   </sheetData>
@@ -1102,149 +1102,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
+      <c r="A1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
     </row>
     <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="10">
         <v>44044</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3">
         <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J6" s="6">
         <v>12</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.2">
@@ -1255,37 +1255,37 @@
         <v>43901</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="10">
         <v>44045</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3">
         <v>22</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J7" s="6">
         <v>22</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" x14ac:dyDescent="0.2">
@@ -1293,40 +1293,40 @@
         <v>500</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="10">
         <v>44044</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" s="3">
         <v>24</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J8" s="6">
         <v>24</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.2">
@@ -1334,40 +1334,40 @@
         <v>500</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="10">
         <v>44044</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3">
         <v>56</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J9" s="6">
         <v>56</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.2">
@@ -1375,40 +1375,40 @@
         <v>500</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="10">
         <v>44045</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="3">
         <v>72</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="6">
         <v>73</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1442,210 +1442,210 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="25"/>
+      <c r="A1" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="44"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="28"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="47"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="28"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="47"/>
     </row>
     <row r="4" spans="1:18" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="30"/>
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="49"/>
     </row>
     <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="43" t="s">
+      <c r="A5" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="43" t="s">
+      <c r="H5" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="I5" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="J5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="K5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="L5" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L5" s="44" t="s">
+      <c r="M5" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="44" t="s">
+      <c r="N5" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="N5" s="44" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
     </row>
     <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="45"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="45"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="45"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A11"/>
@@ -1739,652 +1739,652 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32" t="s">
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+    </row>
+    <row r="2" spans="1:28" ht="57" x14ac:dyDescent="0.45">
+      <c r="A2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-    </row>
-    <row r="2" spans="1:28" ht="57" x14ac:dyDescent="0.45">
-      <c r="A2" s="33" t="s">
+      <c r="D2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="33" t="s">
+      <c r="E2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="F2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="G2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="H2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="I2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="J2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="K2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="L2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="M2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="N2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="O2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="33" t="s">
+      <c r="P2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="33" t="s">
+      <c r="Q2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="33" t="s">
+      <c r="R2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="33" t="s">
+      <c r="S2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="33" t="s">
+      <c r="T2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="33" t="s">
+      <c r="U2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="33" t="s">
+      <c r="V2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="33" t="s">
+      <c r="W2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="33" t="s">
+      <c r="X2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="X2" s="33" t="s">
+      <c r="Y2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="Y2" s="33" t="s">
+      <c r="Z2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="Z2" s="33" t="s">
+      <c r="AA2" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AB2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AB2" s="33" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A3" s="41"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="42"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="36"/>
-      <c r="AB4" s="36"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A5" s="34"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="36"/>
-      <c r="AB5" s="36"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A6" s="34"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="36"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A7" s="34"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="16"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="36"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A9" s="34"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="36"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="36"/>
-      <c r="AB10" s="36"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A11" s="34"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-      <c r="AB11" s="36"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
-      <c r="AB12" s="36"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
-      <c r="S13" s="36"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="36"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="36"/>
-      <c r="AB13" s="36"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A14" s="34"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="36"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="16"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A15" s="34"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
-      <c r="S15" s="36"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="36"/>
-      <c r="V15" s="36"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="36"/>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="36"/>
-      <c r="AA15" s="36"/>
-      <c r="AB15" s="36"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="36"/>
-      <c r="AB16" s="36"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="16"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36"/>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="36"/>
-      <c r="Y17" s="39"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="36"/>
-      <c r="AB17" s="36"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A18" s="34"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="36"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
+      <c r="Z18" s="16"/>
+      <c r="AA18" s="16"/>
+      <c r="AB18" s="16"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="36"/>
-      <c r="AB19" s="36"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A20" s="36"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="36"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="36"/>
-      <c r="AB20" s="36"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
